--- a/docs/design/2026-09-10-project-progress/GameXXK_项目进度与验收总表_2026-09-10.xlsx
+++ b/docs/design/2026-09-10-project-progress/GameXXK_项目进度与验收总表_2026-09-10.xlsx
@@ -13,13 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_共享任务交接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_项目进度'!$A$4:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_项目进度'!$A$4:$H$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'01_项目进度'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_完成门槛'!$A$4:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_完成门槛'!$A$4:$D$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'02_完成门槛'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_遗物素材状态'!$A$4:$I$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'03_遗物素材状态'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_共享任务交接'!$A$4:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04_共享任务交接'!$A$4:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'04_共享任务交接'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 03:09 +08:00  |  执行中，未完成  |  本次允许根目录 codex/ui-visual-optimization；其他任务结束后统一提交</t>
+          <t>2026-09-11 03:14 +08:00  |  执行中，未完成  |  本次允许根目录 codex/ui-visual-optimization；其他任务结束后统一提交</t>
         </is>
       </c>
     </row>
@@ -560,27 +560,27 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>已记录，尚未提交</t>
+          <t>21批备份已提交并全部上传</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>当前分支已核对</t>
+          <t>远端 HEAD 004c45fb9e6ceaedf340698bf5cc41391a60f626 已核对</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>stage/commit/push均未执行</t>
+          <t>备份HEAD 004c45fb9e6ceaedf340698bf5cc41391a60f626；19,373文件/8.787GiB</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>其他任务与本任务验收完成后统一提交</t>
+          <t>完成本任务剩余功能后再次提交与上传</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>docs/production/2026-09-10-ui-guidance-localization-goal.md</t>
+          <t>Saved/Codex/UIGuidanceLocalization-20260910/git-backup/state.json</t>
         </is>
       </c>
     </row>
@@ -602,27 +602,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>基础模块已写，未接入全界面</t>
+          <t>文本身份4414；补回53个跨命名空间条目，完整中文卡面气/内与英文AP/MP。29节教学、23步入门已登记；词缀/逐箱报告新增双语。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>冷UBT通过；词库3项通过；UE行为测试待跑</t>
+          <t>Python本地化7/7；独立Academy与双语恢复回归27/27。新增半透明UI/逐箱报告/乘风尚在冷编译。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>独立FText资源、偏好原子写入与变更通知</t>
+          <t>本地化总表13页；装备49、卡牌173、怪物21名称与教学、规则同步。</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>接入设置及界面刷新并验证重启</t>
+          <t>本轮操作式教学、角色机制、退出上限与F10解锁的冷编译/定向行为/实机验证。</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Saved/Codex/ToolsRedesign-20260909/build-reforge-choice.log</t>
+          <t>docs/design/2026-09-10-ui-localization/export-report.json</t>
         </is>
       </c>
     </row>
@@ -644,27 +644,27 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>按用户最新截图改为背包中央页：同945×533宿主、同纸底边缘与关闭位置，取消独立反向放大；关闭恢复原页</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>待验证</t>
+          <t>中央页26/26通过；最新97.91秒冷UBT通过；DPI虚拟化补偿后中英50/75/100真实鼠标点击及设置边缘实拍通过。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>旧重置按钮仍在，尚未改造</t>
+          <t>设置共用背包945×533中央页、关闭返回原页；已保存并正常退出最新真实玩家，最新备份170317。</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>删除旧入口，加入语言/帮助与独立阅读布局</t>
+          <t>复拍最新无底图折叠图标，后续完整存档管理仍待实现。</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Source/GameXXK/Private/UI/GameXXKDesktopTrainingWorkbenchWidget.cpp</t>
+          <t>Saved/Codex/UIGuidanceLocalization-20260910/ui-review/settings-matrix.json</t>
         </is>
       </c>
     </row>
@@ -681,32 +681,32 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>已建立界面覆盖清单</t>
+          <t>用户明确全屏半透明黑色遮罩、当前按钮/功能镂空，白字说明无局部底框</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>遮罩绘制与强制输入模式解耦；桌面引导移到全窗口根节点并扩展原生窗口区域；界面/战斗教程移除局部底框。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>待验证</t>
+          <t>最终21/21引导检查通过；中文100%按钮与50%功能格/整块设置面板镂空已实拍，玩家真实推进完23步。英文恢复提示已观察，完整多语言逐页视觉覆盖仍待继续。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>旧GuideRegistry缺少多数桌面目标</t>
+          <t>进度复用CompletedGuideStepIds版本化UI.Basics.V1；F1简短上下文说明仍保留。</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>新增帮助目标、关闭/跳过/复习与状态保护</t>
+          <t>整理当前试玩进度与证据，继续未覆盖页面的视觉复核。</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>docs/production/2026-09-10-ui-guidance-localization-goal.md</t>
+          <t>docs/production/2026-09-11-fullscreen-guide-mask.md</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>动态整句、分号分行、宝石完整句、两词装备名及套装Pill、APMPHP与Auto已冷编译；当前工具模式曾被格式化源串回退为中文，已通过独立ModeLabel修正待编译。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>待验证</t>
+          <t>格式化身份/中文语义分号边界29/29；卡名/数量/宝石/工具上一批38/38。宝石中英及纯色英文Pill已实拍；全部Tooltip尚未完整验收。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>分离语义与显示、刷新缓存、复测文本宽度与材质</t>
+          <t>继续实际卡牌普通/Shift/Ctrl与品质Shader、遗物及新增教程逐页复核。</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -770,27 +770,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>独立定义已编译，旧31件目录未切换</t>
+          <t>30件运行时效果、延迟动作账本和46件目录已接入并冷编译通过</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>定义/译文同步检查通过；机制未测试</t>
+          <t>9/9基础回归；新增7/7含真实5牌、无效条件、真实存档限次、待选胜负顺序通过</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>保留16普通/特殊，目标总目录46</t>
+          <t>格挡/反击复用真实反应记录；主动作证据与遗物追加结果分开</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>实现真实联动、次数账本与完整结算测试</t>
+          <t>更多职业/阶段/次数联动、平衡对照与UI视觉验收</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>docs/design/2026-09-10-relic-redesign/runtime-contract.md</t>
+          <t>Saved/Codex/UIGuidanceLocalization-20260910/relic-edge-fixed-tests.json</t>
         </is>
       </c>
     </row>
@@ -812,22 +812,22 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>制作中，未导入UE</t>
+          <t>45张已生成并导入UE</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>按manifest动态统计</t>
+          <t>45/45尺寸透明边缘哈希通过；冷重启加载45/45通过</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>21/45 已整理透明图；0/45 已导入</t>
+          <t>45/45 已整理透明图；45/45 已导入</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>完成全部重绘、透明边缘与小尺寸审核、MCP导入</t>
+          <t>中英遗物卡面与品质shader实机核对</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>地图任务纸底已修；本轮Tooltip未接入</t>
+          <t>已接入代码，等待实机验证</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>已有最终基线实拍，本轮待验证</t>
+          <t>路线摘要/Tooltip结构UE检查通过，实机悬停待验证</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>不再使用旧裁边截图作为现状</t>
+          <t>右侧8段灰字和底部说明已移入tooltip，恢复子项命中</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Saved/RouteNodeArt/map-verified-w6.png</t>
+          <t>Saved/Diagnostics/TalentUpgradeUsability/build-fixed.log</t>
         </is>
       </c>
     </row>
@@ -896,17 +896,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>完整讨伐已冷编译通过，后续存档修复待编译</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>待验证</t>
+          <t>9/9核心回归通过（章间保持/准确收益/票及箱）；真实MVP全三章仍待验收</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>原27关保持，目标新增3个3-4</t>
+          <t>已发现旧生成路线遇敌顺序错配、所有Boss提前终结、无票自动挂机边界</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>docs/production/2026-09-10-ui-guidance-localization-goal.md</t>
+          <t>Saved/Codex/UIGuidanceLocalization-20260910/hunt-full-and-new-save-red-tests.json</t>
         </is>
       </c>
     </row>
@@ -933,22 +933,22 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>三品质映射、首通及失败不耗已确认；箱内分配待答</t>
+          <t>用户确认：按箱来源难度给品质；2%/8%命中时替代原奖励</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>来源品质与替代掉落、首通/旧档补发、预留/成功扣票、满包待入库已接源码</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>待验证</t>
+          <t>首通一次发放、满包待入库、替代掉落与来源、成功扣票/退出保票核心检查通过；整体持久化未完成</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>普通2%、高级8%掉落口径待明确</t>
+          <t>先判断出令，命中仅1令；未命中才生成原装备/宝石/材料</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -975,12 +975,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>红金新箱、全部箱图重绘；品质表待答</t>
+          <t>品质表已批准：高级90/8/1.5/0.5；讨伐60/32/6/2</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>第三箱展开/折叠UI、左右键、实时计数、结算箱与令显示已写，待编译</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>当前高级箱装备/宝石品质固定Rare</t>
+          <t>两张品质表为装备/宝石条件概率；出令替代原奖励</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>定义4倍品质概率，接入左右键与全部宝箱美术</t>
+          <t>接入概率表、第三箱区域与左右键</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Source/GameXXK/Private/GameXXKTrainingChestRules.cpp</t>
+          <t>docs/design/2026-09-10-hunt-stage-design/hunt-design.json</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>未接入</t>
+          <t>HP/攻击/防御倍率与旧伤害去重已冷编译，实际困难/地狱行为待回归</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>必须避免与旧伤害倍率重复乘算</t>
+          <t>新战斗显式保存属性已含难度标记，保留Hard/Hell阶段；旧战斗快照维持原语义</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>目前仅基础源随共享UBT通过</t>
+          <t>联合冷UBT455.01秒通过；独立18866定向27项25通过/2旧迁移快照比较待修</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>不以基础编译代替整体功能验收</t>
+          <t>主线另有21/21通过；图形GUI目前由主线处理用户新档和实机，根任务不接管</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1126,12 +1126,306 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>docs/production/2026-09-10-ui-guidance-localization-goal.md</t>
+          <t>Saved/Codex/UIGuidanceLocalization-20260910/hunt-training-save-regression-first.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>G7Save</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>挂机游戏完整存档与异常恢复</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>用户新增要求；已完成第一轮源码审计与设计矩阵</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>可靠写入/3备份、离线时钟/事务、开箱领奖保存已冷编译；自动保存/精确挂机快照/完整存档UI仍未实现</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>真实任务入战又发现无key FText首次序列化导致CRC误报；主线任务已联合加规范化副本与实际活动战斗磁盘回归，23/23通过；未宣称完整挂机存档已完成</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>保留现有CRC兼容；Write先引擎内存序列化/读回再封装。自动保存/完整挂机快照/UI仍待做。</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>按设计补齐并完成存档专项验收</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Saved/Codex/UIGuidanceLocalization-20260910/hunt-full-and-new-save-red-tests.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>G3A</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>角色职业机制教学</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>用户最新裁决：独立课程遭遇，不补历练来源关卡，与历练地图/难度/门票/奖励解耦。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>角色最大HP300、开场210用于治疗；怪物最大180/240/300、ATK12。主角演示辅助伙伴为刀客，所有借用角色ATK70/DEF35；土司合击正确归入教学伤害。持续指引保留。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>最终79.45秒冷UBT、Academy6/6通过，覆盖29节目标/胜利/HP上限；主角三节分别2、3、1回合结束。此前三节实机通关/奖励/返回已验证，当前新数值待实机短确认。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>目标完成后的全队练习持续推荐；动画/布局过渡保留可見区域；白字避开意图、遮罩覆盖完整viewport。</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>其余12门课程完整实机覆盖及后续用户体验调整。</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>docs/production/2026-09-11-academy-short-demo.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>G3F</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>F10关卡与任务测试入口</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>用户要求解锁所有关卡、所有任务，便于直接测试后续剧情</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>两个首页按钮和同名JSON命令；仅临时旁路入口，复用Dev保护和恢复，不序列化不补发奖励。</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>TemporaryProgressUnlocks通过：30关/61任务入口、无奖励、无存档泄漏、恢复检查；相邻5主线检查通过。</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>用户说明其他任务均已完成，不再跨任务发消息；F10入口保留临时会话保护。</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>F10真实窗口按钮点击验收。</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/Tests/GameXXKDevWorkbenchTest.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>G3E</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>退出离线奖励简短提示</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>未解锁仅提示天赋解锁离线奖励；已解锁分别显示宝箱/金币/经验上限</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>读取三个实际天赋Projection上限，中文英文支持小时/分/秒。</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>中英六场景已通过，含24时28分48秒等不同上限；实际窗口排版待复核。</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>无取整丢失，退出保存和取消流程保持。</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>回归和实机小窗排版。</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/Tests/GameXXKExitOfflineHintTest.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>G4M</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>宝箱材料到工具闭环</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>用户开30多个箱后工具材料为0；保持概率，修正存储来源</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>工具从背包和仓库共同计数并原位扣料；分解保持材料堆位置；开箱具体收据中英已接入。</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>12场景全部通过：3箱型×2材料×2语言，真实开箱到UI与消费、存盘失败、末枚耗尽、分解原位增量、数量刷新。相邻工具/经济/宝箱检查通过。</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>真实仓库20石/19砂原因已确认；实机工具显示20石；用户后续整理与开箱已批准保留并写入正式存档。</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>真实窗口验证材料数量与工具消费，保护真档。</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>docs/production/2026-09-10-stored-tool-materials.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>G4R</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>逐箱掉落报告</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>每箱独立报告，批量每箱一条，完整具体掉落中英配齐</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>每个成功开箱产生稳定收据和独立报告；按当前语言重新构建具体名称/数量/品质/等级/去向，长信息放悬停。</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>逐箱报告检查通过：批量30箱与逐次30箱内容次序相同、30条真实UI历史、中文生成后切英文、保存失败无虚假报告且宝箱保留。</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>早期中文残留告警实际为测试遍历临时FText产生的悬空字符串误报，已纠正；历史仍沿用200条界面消息，不属于跨重启日志。</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>消息区真实悬停视觉复核；跨重启日志随完整存档目标继续。</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/Tests/GameXXKChestReceiptsTest.cpp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>G4W</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>追风乘风与随机资源词缀退休</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>用户确认固定1%、逐张递增、同名正常叠加；按推荐移除随机抽牌/气力/减费/计数</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>乘风固定1%已接真实伤害。5项随机资源词缀退休；旧装备定向转换，强化/孔/归属/其他词缀保留。洗炼使用同一候选池决定启用，窄行短标签、完整白字江湖体Tooltip。</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>核心5/5、相邻69/69通过：逐张与同名叠加、火/冰/雷/物理/重箭、重放不计数/回合重置、两件实际投影、十品质生成洗炼、旧档和待选结果转换。</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>乘风及产甲已生效；其余24项分系词缀的未实现状态保留在总表，不冒充已接入。</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>实际工具窄行与完整Tooltip视觉复核；其余词缀独立继续审查。</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>docs/design/2026-09-11-affix-wind-ramp.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H18"/>
+  <autoFilter ref="A4:H25"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -1147,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1711,17 +2005,83 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>自动保存、手动槽位、正常退出保存和损坏备份恢复均可从纯2D界面使用；失败不假报成功、不丢弃原有效档。</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>最终通过后更新勾选及证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>挂机与三章挑战完整运行态、随机种子、遗物限次、未领收益及票箱事务均可真实中断后恢复。</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>最终通过后更新勾选及证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>离线解锁、分类收益上限、时间回拨、重复读档/领取、写入失败、旧档迁移和开发会话隔离全部有通过证据。</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>最终通过后更新勾选及证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>未完成</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
           <t>所有相关任务结束后才统一提交推送，远端 commit 与本地一致。</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>最终通过后更新勾选及证据</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D28"/>
+  <autoFilter ref="A4:D31"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -1845,7 +2205,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1892,7 +2252,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1939,7 +2299,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1986,7 +2346,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -2033,7 +2393,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -2080,7 +2440,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -2127,7 +2487,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -2174,7 +2534,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -2221,7 +2581,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -2268,7 +2628,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -2315,7 +2675,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -2362,7 +2722,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -2409,7 +2769,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -2456,7 +2816,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -2503,7 +2863,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2550,7 +2910,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2597,7 +2957,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2644,7 +3004,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -2691,7 +3051,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2738,7 +3098,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2785,7 +3145,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
+          <t>已导入</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2822,21 +3182,29 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_RiverPearl.png</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>22d2d4e19aaa45a746268aab4f49a67492ab3dc7abca26fae62f0350a81ba707</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -2861,21 +3229,29 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_CandleStub.png</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>221ae63c237b079fe56c97176c248c143f9aee1c73cf7f5cf728682362a34536</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2900,21 +3276,29 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_FoxMask.png</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>d87fb60ea8da3a6ec1aeb282038eee8e6fbc56129496ff1078e922d7a3bd08a5</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -2939,21 +3323,29 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_StoneLion.png</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>47464895d79c6d3d8c38e945a9b8232f0b3d5ce9e34eb6ad0f8e4c281e59bc76</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -2978,21 +3370,29 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_WineCup.png</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>f13318554c2d1505ece3c2872042cbccb8a131252922ec33b0a4711a3a560488</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -3017,21 +3417,29 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_HerbBasket.png</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>f04b979d4e1cc627b54d122ce03232a2125e2c7c77fcc31fdc135f1af3662059</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -3056,21 +3464,29 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_PaperCrane.png</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>0ab67b0d37fecfc8e2a7e444669aced563a33914f0745b829dc1607669277b21</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -3095,21 +3511,29 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_BrokenArrow.png</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>7db85c7a5bfd222e5db9538e2f7a175bd0eba705f5426a1925b7fe714ddc2959</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3134,21 +3558,29 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_MoonDisc.png</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>e03fc85b9d6226ea09e8f7d764af9cdc58fde7a7f275c17f55495c4d5381b298</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -3173,21 +3605,29 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_BloodInkSeal.png</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>e373316d54ae73354bdc0a6edd9dd49292578359491cd24af243caf12acf32e1</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -3212,21 +3652,29 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_StormChime.png</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>4610aea9fc1075afffb1571e2d9af2d13c7474ce174dbcd687aea66127a56f39</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -3251,21 +3699,29 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_FlameCenser.png</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>23c89920e88d5de27404aaa564a8a43cd1fe9e4914edfd325587fe7bb7d1aafc</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -3290,21 +3746,29 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_HunterQuiver.png</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>aba3438522f12cc0f6667d251753d6ffebb0932d8de5f576c2d9fa61c7a5b77a</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -3329,21 +3793,29 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_MoonDewVial.png</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>91fca0bd6269f364bbccbc4d8a1bc6a45d5905a0ba907cc301fe1acdf103cf00</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -3368,21 +3840,29 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_WarBanner.png</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>5beef82012a5ffefcbe290f3090d5dcffe32acc44a8a00fa5c4e1601d2caf4e5</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -3407,21 +3887,29 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_AmberPestle.png</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>0cab4737d0b507c6904900ee57951597ba956f927910eeff56909c8d8e4bc851</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -3446,21 +3934,29 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_TwinJade.png</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>f45a676426e62eb1690291ec947d35c715f4c827acf7a50a6fac3031532de97c</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -3485,21 +3981,29 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_SilkFan.png</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>517e493a453d15a697a7005c10e9e73b7ef14a5d38604efe7f40f55e414ef9f6</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -3524,21 +4028,29 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_ObsidianScale.png</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>269b4302adabcbf68111eb50d18642067b84805dc3f7bb3ef12022fb50771c5f</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -3563,21 +4075,29 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_BloodMoonBlade.png</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>40ac78fa2b00ec8adc4fc251765ee5d1e3e3439dd363ca48e0c57be4472af43f</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -3602,21 +4122,29 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_PhoenixCauldron.png</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>3044e4aca226a97412482a34139107c8eebac572a5acae5ec288ddadea2a3216</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3641,21 +4169,29 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_StarAbacus.png</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>20516f3802f25d8d0145e617f05878f79a3bad695953198e8efaec6a09093fcf</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -3680,21 +4216,29 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_DragonCarapace.png</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>3f397cee05b4e60ebb8c29d109253987af4d9459977692c8059f81b9297fb6e5</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -3719,21 +4263,29 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>待完成</t>
+          <t>512透明图已整理</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>待复核</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>未导入</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr"/>
-      <c r="I49" s="4" t="inlineStr"/>
+          <t>已导入</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>SourceArt/UI/Relics/gemstyle-20260910/icons/T_Relic_ThunderSeal.png</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>b98fb7be28023bbce0d627c51658ca70fbe9bebe1a16205124fe19fa33645884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:I49"/>
@@ -3752,7 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3811,7 +4363,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>已完成并冻结</t>
+          <t>用户明确已完成；本任务不再发送消息</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3838,7 +4390,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>已完成并冻结</t>
+          <t>用户明确已完成；本任务不再发送消息</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -3865,27 +4417,81 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>最终实拍进行中，等待交接</t>
+          <t>用户明确已完成；本任务不再发送消息</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>主线/对白</t>
+          <t>六章61节点全文与主线显示；最新玩家快照恢复</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>以其最终验收为准</t>
+          <t>31/31英文及主线回归通过；代表实拍中断后恢复最新真实快照，尚待实拍收尾</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>任务01a08172-043d-75e0-a149-f8895de07b04</t>
+          <t>Saved/StorySystem/Localization/save-audit-after-restart.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>统计天赋金币需求</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>用户明确已完成；本任务不再发送消息</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>天赋/属性/tooltip</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>25/25；真实连续5次升级及2种tooltip实拍通过</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Saved/Diagnostics/TalentUpgradeUsability/build-fixed.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>重制装备图标画风</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>用户明确已完成；本任务不再发送消息</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>宝石风格装备图标；GemstyleKeyframes默认0的2单位8/10帧试验</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Pilot1/1及UnitVisual3/3通过；图形窗口改为协调独占，不得再打断玩家保护会话</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Saved/Diagnostics/GemstyleKeyframePilot-20260910</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E7"/>
+  <autoFilter ref="A4:E9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/design/2026-09-10-project-progress/GameXXK_项目进度与验收总表_2026-09-10.xlsx
+++ b/docs/design/2026-09-10-project-progress/GameXXK_项目进度与验收总表_2026-09-10.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_项目进度" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_完成门槛" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_遗物素材状态" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_共享任务交接" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="01_项目进度" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_完成门槛" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_遗物素材状态" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_共享任务交接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_项目进度'!$A$4:$H$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_项目进度'!$A$4:$H$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'01_项目进度'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02_完成门槛'!$A$4:$D$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'02_完成门槛'!$1:$4</definedName>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 03:14 +08:00  |  执行中，未完成  |  本次允许根目录 codex/ui-visual-optimization；其他任务结束后统一提交</t>
+          <t>2026-09-11 17:07 +08:00  |  执行中，未完成  |  本次允许根目录 codex/ui-visual-optimization；其他任务结束后统一提交</t>
         </is>
       </c>
     </row>
@@ -1424,8 +1424,50 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>G5P</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>三箱品质概率与宇宙获取路径</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>用户批准三箱一起重列：基点域每列精确10000，珍稀及以上严格1:4:16。讨伐箱采用乙方案：宇宙16bp、天界80bp、登神40bp，是唯一直出顶三档的来源，顶端逐级递减不倒挂；普通箱止于至宝、高级箱止于超凡。九合一采用提案B：每档只前进一档或保持原品质，无跨档跳变，成功率单一平滑递减100/100/100/90/85/80/75/70/60%</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>ResolveLootQuality 改为十档四列（含来源难度）；OpenOneInternal 对普通箱也掷真实随机品质；ToolCombineProbability 改为提案B；设计总表sheet02+sheet04、运行时契约、游戏内 Chest.*.Odds 文本与本地化总表同步</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>冷UBT通过（首次因编辑器占用DLL链接失败，关闭后通过）；GameXXK.Hunt 10/10、Training 50/50、ToolsRedesign 14/14、Localization 21/21；本地化目录测试7/7；10桶609项回归591通过、失败集与改动前完全一致（18项既有红项）</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>实测全队18件宇宙约1.84年（承诺1-2年），其中直出贡献约84%；非地狱讨伐箱路径约11.3年，故地狱讨伐是关键</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>开箱与九合一实机手感复核；用新经济重跑744场矩阵重新判定地狱3-3/3-4定位</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>docs/production/2026-09-11-three-chest-quality-table.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H25"/>
+  <autoFilter ref="A4:H26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
